--- a/fpga/projects/bad_timing3.xlsx
+++ b/fpga/projects/bad_timing3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -56,73 +56,82 @@
     <t>Clock Uncertainty</t>
   </si>
   <si>
-    <t>Path 250</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_divclk_reset/U0/ACTIVE_LOW_PR_OUT_DFF[0].FDRE_PER_N/C</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_enable_m1_reg[1]/CLR</t>
-  </si>
-  <si>
-    <t>clk_div_sel_1_s</t>
+    <t>Path 129</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[4]/C</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[13]/D</t>
+  </si>
+  <si>
+    <t>rx_clk</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Path 251</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_enable_reg[1]/CLR</t>
-  </si>
-  <si>
-    <t>Path 252</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_enable_m1_reg[2]/CLR</t>
-  </si>
-  <si>
-    <t>Path 253</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_enable_reg[2]/CLR</t>
-  </si>
-  <si>
-    <t>Path 254</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_req_t_m1_reg/CLR</t>
-  </si>
-  <si>
-    <t>Path 255</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_req_t_m2_reg/CLR</t>
-  </si>
-  <si>
-    <t>Path 256</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_req_t_m3_reg/CLR</t>
-  </si>
-  <si>
-    <t>Path 257</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_req_t_reg/CLR</t>
-  </si>
-  <si>
-    <t>Path 258</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_rinit_reg[0]/CLR</t>
-  </si>
-  <si>
-    <t>Path 259</t>
-  </si>
-  <si>
-    <t>i_system_wrapper/system_i/util_ad9361_adc_fifo/inst/dout_req_cnt_reg[0]/CLR</t>
+    <t>Path 130</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[15]/D</t>
+  </si>
+  <si>
+    <t>Path 131</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[14]/D</t>
+  </si>
+  <si>
+    <t>Path 132</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[12]/D</t>
+  </si>
+  <si>
+    <t>Path 133</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[9]/D</t>
+  </si>
+  <si>
+    <t>Path 134</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/i_tx_channel_0/i_dds/dds_phase[1].i_dds_2/i_dds_1_0/i_dds_sine/rotation[6].pipe/result_z_reg[12]/C</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/i_tx_channel_0/i_dds/dds_phase[1].i_dds_2/i_dds_1_0/i_dds_sine/rotation[7].pipe/result_x_reg[13]/D</t>
+  </si>
+  <si>
+    <t>Path 135</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[11]/D</t>
+  </si>
+  <si>
+    <t>Path 136</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/i_tx_channel_2/i_dds/dds_phase[1].i_dds_2/i_dds_1_1/i_dds_sine/z0_reg[12]/C</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/i_tx_channel_2/i_dds/dds_phase[1].i_dds_2/i_dds_1_1/i_dds_sine/rotation[0].pipe/result_x_reg[13]/D</t>
+  </si>
+  <si>
+    <t>Path 137</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/dac_rate_cnt_reg[10]/D</t>
+  </si>
+  <si>
+    <t>Path 138</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/i_tx_channel_3/i_dds/dds_phase[1].i_dds_2/i_dds_1_1/i_dds_sine/z0_reg[12]/C</t>
+  </si>
+  <si>
+    <t>i_system_wrapper/system_i/axi_ad9361/inst/i_tx/i_tx_channel_3/i_dds/dds_phase[1].i_dds_2/i_dds_1_1/i_dds_sine/rotation[0].pipe/result_z_reg[12]/D</t>
   </si>
 </sst>
 </file>
@@ -209,7 +218,7 @@
     <col min="8" max="8" width="12.8125" customWidth="true"/>
     <col min="9" max="9" width="11.09375" customWidth="true"/>
     <col min="10" max="10" width="14.0625" customWidth="true"/>
-    <col min="11" max="11" width="17.03125" customWidth="true"/>
+    <col min="11" max="11" width="14.21875" customWidth="true"/>
     <col min="12" max="12" width="17.96875" customWidth="true"/>
     <col min="13" max="13" width="11.09375" customWidth="true"/>
     <col min="14" max="14" width="17.65625" customWidth="true"/>
@@ -264,13 +273,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="n" s="4">
-        <v>-10.163000106811523</v>
+        <v>-0.0989999994635582</v>
       </c>
       <c r="C2" t="n" s="6">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="D2" t="n" s="6">
-        <v>1706.0</v>
+        <v>31.0</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>15</v>
@@ -279,16 +288,16 @@
         <v>16</v>
       </c>
       <c r="G2" t="n" s="4">
-        <v>17.61988639831543</v>
+        <v>4.112687110900879</v>
       </c>
       <c r="H2" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.9799998998641968</v>
       </c>
       <c r="I2" t="n" s="4">
-        <v>17.039886474609375</v>
+        <v>2.1326873302459717</v>
       </c>
       <c r="J2" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K2" t="s" s="2">
         <v>17</v>
@@ -308,13 +317,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="n" s="4">
-        <v>-10.163000106811523</v>
+        <v>-0.09099999815225601</v>
       </c>
       <c r="C3" t="n" s="6">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="D3" t="n" s="6">
-        <v>1706.0</v>
+        <v>31.0</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>15</v>
@@ -323,16 +332,16 @@
         <v>20</v>
       </c>
       <c r="G3" t="n" s="4">
-        <v>17.61988639831543</v>
+        <v>4.104686260223389</v>
       </c>
       <c r="H3" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.9719998836517334</v>
       </c>
       <c r="I3" t="n" s="4">
-        <v>17.039886474609375</v>
+        <v>2.1326873302459717</v>
       </c>
       <c r="J3" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K3" t="s" s="2">
         <v>17</v>
@@ -352,13 +361,13 @@
         <v>21</v>
       </c>
       <c r="B4" t="n" s="4">
-        <v>-10.156000137329102</v>
+        <v>-0.014999999664723873</v>
       </c>
       <c r="C4" t="n" s="6">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="D4" t="n" s="6">
-        <v>1706.0</v>
+        <v>31.0</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>15</v>
@@ -367,16 +376,16 @@
         <v>22</v>
       </c>
       <c r="G4" t="n" s="4">
-        <v>17.611486434936523</v>
+        <v>4.0286865234375</v>
       </c>
       <c r="H4" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.8960000276565552</v>
       </c>
       <c r="I4" t="n" s="4">
-        <v>17.03148651123047</v>
+        <v>2.1326873302459717</v>
       </c>
       <c r="J4" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>17</v>
@@ -396,13 +405,13 @@
         <v>23</v>
       </c>
       <c r="B5" t="n" s="4">
-        <v>-10.156000137329102</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C5" t="n" s="6">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="D5" t="n" s="6">
-        <v>1706.0</v>
+        <v>31.0</v>
       </c>
       <c r="E5" t="s" s="2">
         <v>15</v>
@@ -411,16 +420,16 @@
         <v>24</v>
       </c>
       <c r="G5" t="n" s="4">
-        <v>17.611486434936523</v>
+        <v>4.008686542510986</v>
       </c>
       <c r="H5" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.8760000467300415</v>
       </c>
       <c r="I5" t="n" s="4">
-        <v>17.03148651123047</v>
+        <v>2.1326873302459717</v>
       </c>
       <c r="J5" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>17</v>
@@ -440,13 +449,13 @@
         <v>25</v>
       </c>
       <c r="B6" t="n" s="4">
-        <v>-10.156000137329102</v>
+        <v>0.06300000101327896</v>
       </c>
       <c r="C6" t="n" s="6">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="D6" t="n" s="6">
-        <v>1706.0</v>
+        <v>31.0</v>
       </c>
       <c r="E6" t="s" s="2">
         <v>15</v>
@@ -455,16 +464,16 @@
         <v>26</v>
       </c>
       <c r="G6" t="n" s="4">
-        <v>17.611486434936523</v>
+        <v>3.9866766929626465</v>
       </c>
       <c r="H6" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.8630000352859497</v>
       </c>
       <c r="I6" t="n" s="4">
-        <v>17.03148651123047</v>
+        <v>2.1236765384674072</v>
       </c>
       <c r="J6" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K6" t="s" s="2">
         <v>17</v>
@@ -484,31 +493,31 @@
         <v>27</v>
       </c>
       <c r="B7" t="n" s="4">
-        <v>-10.156000137329102</v>
+        <v>0.07100000232458115</v>
       </c>
       <c r="C7" t="n" s="6">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D7" t="n" s="6">
-        <v>1706.0</v>
+        <v>43.0</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n" s="4">
-        <v>17.611486434936523</v>
+        <v>3.7124104499816895</v>
       </c>
       <c r="H7" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.8680000305175781</v>
       </c>
       <c r="I7" t="n" s="4">
-        <v>17.03148651123047</v>
+        <v>1.8444108963012695</v>
       </c>
       <c r="J7" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K7" t="s" s="2">
         <v>17</v>
@@ -525,34 +534,34 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="n" s="4">
-        <v>-10.156000137329102</v>
+        <v>0.07100000232458115</v>
       </c>
       <c r="C8" t="n" s="6">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="D8" t="n" s="6">
-        <v>1706.0</v>
+        <v>31.0</v>
       </c>
       <c r="E8" t="s" s="2">
         <v>15</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n" s="4">
-        <v>17.611486434936523</v>
+        <v>3.9786760807037354</v>
       </c>
       <c r="H8" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.8550000190734863</v>
       </c>
       <c r="I8" t="n" s="4">
-        <v>17.03148651123047</v>
+        <v>2.1236765384674072</v>
       </c>
       <c r="J8" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>17</v>
@@ -569,34 +578,34 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="n" s="4">
-        <v>-10.156000137329102</v>
+        <v>0.0949999988079071</v>
       </c>
       <c r="C9" t="n" s="6">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D9" t="n" s="6">
-        <v>1706.0</v>
+        <v>43.0</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n" s="4">
-        <v>17.611486434936523</v>
+        <v>3.914689064025879</v>
       </c>
       <c r="H9" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>2.1530001163482666</v>
       </c>
       <c r="I9" t="n" s="4">
-        <v>17.03148651123047</v>
+        <v>1.7616890668869019</v>
       </c>
       <c r="J9" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>17</v>
@@ -613,34 +622,34 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" t="n" s="4">
-        <v>-10.156000137329102</v>
+        <v>0.1469999998807907</v>
       </c>
       <c r="C10" t="n" s="6">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="D10" t="n" s="6">
-        <v>1706.0</v>
+        <v>31.0</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>15</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n" s="4">
-        <v>17.611486434936523</v>
+        <v>3.9026763439178467</v>
       </c>
       <c r="H10" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.7790000438690186</v>
       </c>
       <c r="I10" t="n" s="4">
-        <v>17.03148651123047</v>
+        <v>2.1236765384674072</v>
       </c>
       <c r="J10" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>17</v>
@@ -657,34 +666,34 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n" s="4">
-        <v>-10.04699993133545</v>
+        <v>0.15399999916553497</v>
       </c>
       <c r="C11" t="n" s="6">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D11" t="n" s="6">
-        <v>1706.0</v>
+        <v>43.0</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n" s="4">
-        <v>17.50136375427246</v>
+        <v>3.6508617401123047</v>
       </c>
       <c r="H11" t="n" s="4">
-        <v>0.5800000429153442</v>
+        <v>1.945000171661377</v>
       </c>
       <c r="I11" t="n" s="4">
-        <v>16.921363830566406</v>
+        <v>1.705861210823059</v>
       </c>
       <c r="J11" t="n" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>17</v>
